--- a/exports/trend_1d/SWIGGY_full_report.xlsx
+++ b/exports/trend_1d/SWIGGY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>17.86</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H2" t="n">
-        <v>492.3</v>
+        <v>463.1</v>
       </c>
       <c r="I2" t="n">
         <v>489.4177085581879</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.58</v>
+        <v>-1.63</v>
       </c>
       <c r="L2" t="n">
         <v>3.43</v>
@@ -555,7 +578,7 @@
         <v>3.08</v>
       </c>
       <c r="N2" t="n">
-        <v>4.29</v>
+        <v>5.93</v>
       </c>
       <c r="O2" t="n">
         <v>-4.22</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>20.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H3" t="n">
-        <v>333.2</v>
+        <v>362.75</v>
       </c>
       <c r="I3" t="n">
         <v>352.9050951265384</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K3" t="n">
-        <v>28.05</v>
+        <v>21.67</v>
       </c>
       <c r="L3" t="n">
         <v>11.16</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.72</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H4" t="n">
-        <v>417.95</v>
+        <v>409.95</v>
       </c>
       <c r="I4" t="n">
         <v>415.5553253254334</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K4" t="n">
-        <v>15.22</v>
+        <v>13.01</v>
       </c>
       <c r="L4" t="n">
         <v>7.62</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>6</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H5" t="n">
-        <v>333.7</v>
+        <v>355.75</v>
       </c>
       <c r="I5" t="n">
         <v>353.2225082161432</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K5" t="n">
-        <v>18.6</v>
+        <v>13.22</v>
       </c>
       <c r="L5" t="n">
         <v>5.87</v>
@@ -726,7 +785,7 @@
         <v>4.11</v>
       </c>
       <c r="N5" t="n">
-        <v>4.97</v>
+        <v>6.61</v>
       </c>
       <c r="O5" t="n">
         <v>-1.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>15.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H6" t="n">
-        <v>301.75</v>
+        <v>289</v>
       </c>
       <c r="I6" t="n">
         <v>300.8922594642947</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>-15.18</v>
+        <v>-18.76</v>
       </c>
       <c r="L6" t="n">
-        <v>16.13</v>
+        <v>19.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0.96</v>
+        <v>3.83</v>
       </c>
       <c r="N6" t="n">
-        <v>3.78</v>
+        <v>4.23</v>
       </c>
       <c r="O6" t="n">
         <v>6.61</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.66</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="H7" t="n">
-        <v>248.37</v>
+        <v>266.27</v>
       </c>
       <c r="I7" t="n">
         <v>263.7130998475139</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K7" t="n">
-        <v>14.06</v>
+        <v>7.87</v>
       </c>
       <c r="L7" t="n">
         <v>5.95</v>
@@ -840,7 +923,7 @@
         <v>4.34</v>
       </c>
       <c r="N7" t="n">
-        <v>6.6</v>
+        <v>7.21</v>
       </c>
       <c r="O7" t="n">
         <v>-4.23</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.03</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H8" t="n">
-        <v>264.85</v>
+        <v>256</v>
       </c>
       <c r="I8" t="n">
         <v>263.2682474012039</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.53</v>
+        <v>-3.86</v>
       </c>
       <c r="L8" t="n">
         <v>8.92</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -957,6 +1064,14 @@
       <c r="Q9" t="n">
         <v>21</v>
       </c>
+      <c r="R9" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1903,7 +2018,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93.59999999999999</v>
+        <v>95.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1913,7 +2028,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -1923,7 +2038,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
@@ -1933,7 +2048,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1943,7 +2058,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133.5</v>
+        <v>134.5</v>
       </c>
     </row>
     <row r="10">
@@ -1953,7 +2068,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143.8</v>
+        <v>144.8</v>
       </c>
     </row>
     <row r="11">
@@ -1993,7 +2108,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.26</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="15">
@@ -2003,7 +2118,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.02</v>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="16">
@@ -2013,7 +2128,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20.24</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="17">
@@ -2023,7 +2138,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28.05</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="18">
@@ -2033,7 +2148,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="19">
@@ -2043,7 +2158,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.44</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="20">
@@ -2063,7 +2178,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.13</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="22">
@@ -2093,7 +2208,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.83</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="25">
@@ -2113,7 +2228,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.7</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="27">
@@ -2133,7 +2248,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
